--- a/AAII_Financials/Yearly/ARRPY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ARRPY_YR_FIN.xlsx
@@ -878,7 +878,7 @@
         <v>-122100</v>
       </c>
       <c r="E14" s="3">
-        <v>-210200</v>
+        <v>-85900</v>
       </c>
       <c r="F14" s="3">
         <v>-169100</v>
